--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.51104175659769</v>
+        <v>6.095544285447125</v>
       </c>
       <c r="D2" t="n">
-        <v>55.84011373583753</v>
+        <v>9.074018482073598</v>
       </c>
       <c r="E2" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F2" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.77229516082524</v>
+        <v>8.250497963634103</v>
       </c>
       <c r="D3" t="n">
-        <v>50.54151928695423</v>
+        <v>8.212996884130062</v>
       </c>
       <c r="E3" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F3" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.69420341360018</v>
+        <v>2.22530805471003</v>
       </c>
       <c r="D4" t="n">
-        <v>67.93418226137628</v>
+        <v>11.03930461747365</v>
       </c>
       <c r="E4" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F4" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.81691446255083</v>
+        <v>6.95774860016451</v>
       </c>
       <c r="D5" t="n">
-        <v>33.78743843095502</v>
+        <v>5.490458745030191</v>
       </c>
       <c r="E5" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F5" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.51766039924054</v>
+        <v>7.884119814876589</v>
       </c>
       <c r="D6" t="n">
-        <v>50.04136365671584</v>
+        <v>8.131721594216325</v>
       </c>
       <c r="E6" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F6" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.31857521506199</v>
+        <v>3.301768472447573</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57456214106593</v>
+        <v>5.780866347923214</v>
       </c>
       <c r="E7" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F7" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.92628358499039</v>
+        <v>5.025521082560938</v>
       </c>
       <c r="D8" t="n">
-        <v>32.83841072387703</v>
+        <v>5.336241742630018</v>
       </c>
       <c r="E8" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F8" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.59126480678323</v>
+        <v>4.321080531102275</v>
       </c>
       <c r="D9" t="n">
-        <v>12.59005919202245</v>
+        <v>2.045884618703647</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F9" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.23579103873659</v>
+        <v>5.075816043794696</v>
       </c>
       <c r="D10" t="n">
-        <v>49.07367077877949</v>
+        <v>7.974471501551667</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F10" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.64435297067021</v>
+        <v>5.792207357733909</v>
       </c>
       <c r="D11" t="n">
-        <v>44.66973026175825</v>
+        <v>7.258831167535717</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F11" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.42243331645298</v>
+        <v>7.381145413923609</v>
       </c>
       <c r="D12" t="n">
-        <v>55.18661829695561</v>
+        <v>8.967825473255287</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F12" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.53783883413955</v>
+        <v>6.587398810547677</v>
       </c>
       <c r="D13" t="n">
-        <v>53.06837480257007</v>
+        <v>8.623610905417637</v>
       </c>
       <c r="E13" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F13" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.03024668048799</v>
+        <v>5.204915085579299</v>
       </c>
       <c r="D14" t="n">
-        <v>37.49489962167652</v>
+        <v>6.092921188522435</v>
       </c>
       <c r="E14" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F14" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.29560875909974</v>
+        <v>6.873036423353708</v>
       </c>
       <c r="D15" t="n">
-        <v>56.37161679684043</v>
+        <v>9.160387729486571</v>
       </c>
       <c r="E15" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F15" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.606546454013</v>
+        <v>7.086063798777112</v>
       </c>
       <c r="D16" t="n">
-        <v>56.54144474550818</v>
+        <v>9.18798477114508</v>
       </c>
       <c r="E16" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F16" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.04971665756924</v>
+        <v>6.183078956855002</v>
       </c>
       <c r="D17" t="n">
-        <v>37.60945599528451</v>
+        <v>6.111536599233732</v>
       </c>
       <c r="E17" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F17" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.34302453467417</v>
+        <v>4.118241486884552</v>
       </c>
       <c r="D18" t="n">
-        <v>25.02663334598702</v>
+        <v>4.066827918722891</v>
       </c>
       <c r="E18" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F18" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>50.94537615469844</v>
+        <v>8.278623625138497</v>
       </c>
       <c r="D19" t="n">
-        <v>51.90762870262453</v>
+        <v>8.434989664176486</v>
       </c>
       <c r="E19" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F19" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27925349434253</v>
+        <v>5.245378692830662</v>
       </c>
       <c r="D20" t="n">
-        <v>32.15089399471125</v>
+        <v>5.224520274140579</v>
       </c>
       <c r="E20" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F20" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>23.78877812508614</v>
+        <v>3.865676445326497</v>
       </c>
       <c r="D21" t="n">
-        <v>23.68541124244996</v>
+        <v>3.848879326898119</v>
       </c>
       <c r="E21" t="n">
-        <v>10.06973499728812</v>
+        <v>1.636331937059321</v>
       </c>
       <c r="F21" t="n">
-        <v>13.53721452039696</v>
+        <v>2.199797359564507</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
